--- a/human_resources_forms/010_simple_job_application_form_red_and_responsive--human_resources_forms.xlsx
+++ b/human_resources_forms/010_simple_job_application_form_red_and_responsive--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'it_support'}</t>
+          <t>it_support</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'IT Support'}</t>
+          <t>IT Support</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'software_developer'}</t>
+          <t>software_developer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Software Developer'}</t>
+          <t>Software Developer</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'marketing_specialist'}</t>
+          <t>marketing_specialist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Marketing Specialist'}</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
